--- a/shohta/log/EMMAmeasurement_0912.xlsx
+++ b/shohta/log/EMMAmeasurement_0912.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shohtatakami/github/LeicaAT401_MIT/shohta/log/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB378E14-637F-1247-B926-CEC46622C270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D1C6D6-4827-EB47-8FD9-2B1983D01FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19060" yWindow="-20940" windowWidth="25360" windowHeight="20780" xr2:uid="{9774FBA4-0317-8843-8EC7-CE4746E53017}"/>
+    <workbookView xWindow="19040" yWindow="-20940" windowWidth="25360" windowHeight="20780" xr2:uid="{9774FBA4-0317-8843-8EC7-CE4746E53017}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Point Name</t>
   </si>
@@ -75,6 +75,15 @@
   </si>
   <si>
     <t>SP3</t>
+  </si>
+  <si>
+    <t>EMMA</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>EMMA-Python</t>
   </si>
 </sst>
 </file>
@@ -118,6 +127,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0432FF"/>
+      <color rgb="FF156082"/>
+      <color rgb="FFFFFFFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -127,6 +143,2969 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="1"/>
+              <a:t>R</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0432FF"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>101B</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SC</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SlaveDown</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>MasterDown</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>MasterUp</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>B</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>D</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>SP1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>SP2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SP3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$3:$J$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>4.6282367598905694E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.7934785339948576E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2237359449954965E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.8293622200180835E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.0283931950179976E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.0074943550062017E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.1550001750256342E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2598010389629053E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.2008233259148255E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5900999999757914E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.6301954789923911E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E1DF-A046-87C1-99C9C89141FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="469728063"/>
+        <c:axId val="469590639"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="469728063"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="469590639"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="469590639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="469728063"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="1"/>
+              <a:t>Phi</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10691480665261098"/>
+          <c:y val="0.10990256705716664"/>
+          <c:w val="0.85976343189217264"/>
+          <c:h val="0.83900800204852444"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="156082">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0432FF"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>101B</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SC</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SlaveDown</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>MasterDown</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>MasterUp</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>B</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>D</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>SP1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>SP2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SP3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$3:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-1.4829981570319006E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.1930496379930489E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8.2811809600791264E-6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6.3203795160227116E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-7.6098284598202781E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-6.172312370100741E-6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-3.2784452299594591E-6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-5.5390877697902852E-6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.635021525991931E-5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.7142976760364803E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.4660252090070713E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CD19-BF40-AE45-2A2D8BEA2968}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="469728063"/>
+        <c:axId val="469590639"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="469728063"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="469590639"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="469590639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="469728063"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="1"/>
+              <a:t>Theta</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13565300254661958"/>
+          <c:y val="0.11309951442258073"/>
+          <c:w val="0.85976343189217264"/>
+          <c:h val="0.83900800204852444"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="156082">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0432FF"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>101B</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SC</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SlaveDown</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>MasterDown</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>MasterUp</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>B</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>D</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>SP1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>SP2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SP3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$L$3:$L$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-3.6518110100303147E-6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4415074770043361E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.7290000000366206E-6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9018782090162176E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-3.9270000000701799E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-2.2120164988592705E-7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-8.4359872598582797E-6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2.0678375500793322E-6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.3260995799876412E-5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.4090154619924604E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.115496135015384E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-73C8-2346-8326-2AD1EBE2B9BC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="469728063"/>
+        <c:axId val="469590639"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="469728063"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="469590639"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="469590639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="469728063"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>704850</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABC5C2C1-2D00-C6D8-1367-58FD1EBAB247}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>147675</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>59070</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>177210</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C143AD9-4CF3-EE42-BDA3-6E0DF1502E41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>959883</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{531F6E36-AC15-7147-B270-A105773A79EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -446,75 +3425,452 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D939530-67FE-6A42-8537-37F3303CF5B5}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>5329.3634590000001</v>
+      </c>
+      <c r="C2">
+        <v>2.618401</v>
+      </c>
+      <c r="D2">
+        <v>1.6170329999999999</v>
+      </c>
+      <c r="F2">
+        <v>5328.0177783277804</v>
+      </c>
+      <c r="G2">
+        <v>2.61797915309675</v>
+      </c>
+      <c r="H2">
+        <v>1.6170143574660201</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ref="J2" si="0">B2-F2</f>
+        <v>1.3456806722197143</v>
+      </c>
+      <c r="K2">
+        <f t="shared" ref="K2" si="1">C2-G2</f>
+        <v>4.2184690324997831E-4</v>
+      </c>
+      <c r="L2">
+        <f t="shared" ref="L2" si="2">D2-H2</f>
+        <v>1.8642533979873477E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
+      <c r="B3">
+        <v>17679.969228999998</v>
+      </c>
+      <c r="C3">
+        <v>-2.7786330000000001</v>
+      </c>
+      <c r="D3">
+        <v>1.675446</v>
+      </c>
+      <c r="F3">
+        <v>17679.9229466324</v>
+      </c>
+      <c r="G3">
+        <v>-2.7786181700184298</v>
+      </c>
+      <c r="H3">
+        <v>1.67544965181101</v>
+      </c>
+      <c r="J3">
+        <f>B3-F3</f>
+        <v>4.6282367598905694E-2</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:L13" si="3">C3-G3</f>
+        <v>-1.4829981570319006E-5</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="3"/>
+        <v>-3.6518110100303147E-6</v>
+      </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>4081.56349</v>
+      </c>
+      <c r="C4">
+        <v>-1.4795769999999999</v>
+      </c>
+      <c r="D4">
+        <v>2.042783</v>
+      </c>
+      <c r="F4">
+        <v>4081.4855552146601</v>
+      </c>
+      <c r="G4">
+        <v>-1.47956506950362</v>
+      </c>
+      <c r="H4">
+        <v>2.04273858492523</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J13" si="4">B4-F4</f>
+        <v>7.7934785339948576E-2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="3"/>
+        <v>-1.1930496379930489E-5</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="3"/>
+        <v>4.4415074770043361E-5</v>
+      </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="B5">
+        <v>2982.167445</v>
+      </c>
+      <c r="C5">
+        <v>-3.034624</v>
+      </c>
+      <c r="D5">
+        <v>1.9009229999999999</v>
+      </c>
+      <c r="F5">
+        <v>2982.1552076405501</v>
+      </c>
+      <c r="G5">
+        <v>-3.0346157188190399</v>
+      </c>
+      <c r="H5">
+        <v>1.900927729</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="4"/>
+        <v>1.2237359449954965E-2</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="3"/>
+        <v>-8.2811809600791264E-6</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="3"/>
+        <v>-4.7290000000366206E-6</v>
+      </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>3406.2882030000001</v>
+      </c>
+      <c r="C6">
+        <v>-2.6991420000000002</v>
+      </c>
+      <c r="D6">
+        <v>1.8550580000000001</v>
+      </c>
+      <c r="F6">
+        <v>3406.2599093777999</v>
+      </c>
+      <c r="G6">
+        <v>-2.6990787962048399</v>
+      </c>
+      <c r="H6">
+        <v>1.8550289812179099</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="4"/>
+        <v>2.8293622200180835E-2</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="3"/>
+        <v>-6.3203795160227116E-5</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="3"/>
+        <v>2.9018782090162176E-5</v>
+      </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>9928.4055189999999</v>
+      </c>
+      <c r="C7">
+        <v>-2.840236</v>
+      </c>
+      <c r="D7">
+        <v>1.667843</v>
+      </c>
+      <c r="F7">
+        <v>9928.3752350680497</v>
+      </c>
+      <c r="G7">
+        <v>-2.8402283901715402</v>
+      </c>
+      <c r="H7">
+        <v>1.667846927</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="4"/>
+        <v>3.0283931950179976E-2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>-7.6098284598202781E-6</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="3"/>
+        <v>-3.9270000000701799E-6</v>
+      </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
+      <c r="B8">
+        <v>4395.9759869999998</v>
+      </c>
+      <c r="C8">
+        <v>-2.8695569999999999</v>
+      </c>
+      <c r="D8">
+        <v>1.4346030000000001</v>
+      </c>
+      <c r="F8">
+        <v>4395.9459120564497</v>
+      </c>
+      <c r="G8">
+        <v>-2.8695508276876298</v>
+      </c>
+      <c r="H8">
+        <v>1.43460322120165</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="4"/>
+        <v>3.0074943550062017E-2</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>-6.172312370100741E-6</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="3"/>
+        <v>-2.2120164988592705E-7</v>
+      </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="B9">
+        <v>4361.4975979999999</v>
+      </c>
+      <c r="C9">
+        <v>-2.9942440000000001</v>
+      </c>
+      <c r="D9">
+        <v>1.5698780000000001</v>
+      </c>
+      <c r="F9">
+        <v>4361.4760479982497</v>
+      </c>
+      <c r="G9">
+        <v>-2.9942407215547702</v>
+      </c>
+      <c r="H9">
+        <v>1.56988643598726</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="4"/>
+        <v>2.1550001750256342E-2</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>-3.2784452299594591E-6</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="3"/>
+        <v>-8.4359872598582797E-6</v>
+      </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="B10">
+        <v>4361.2932430000001</v>
+      </c>
+      <c r="C10">
+        <v>-2.840614</v>
+      </c>
+      <c r="D10">
+        <v>1.6160019999999999</v>
+      </c>
+      <c r="F10">
+        <v>4361.2706449896104</v>
+      </c>
+      <c r="G10">
+        <v>-2.8406084609122302</v>
+      </c>
+      <c r="H10">
+        <v>1.61600406783755</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="4"/>
+        <v>2.2598010389629053E-2</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>-5.5390877697902852E-6</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>-2.0678375500793322E-6</v>
+      </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="B11">
+        <v>5658.7651159999996</v>
+      </c>
+      <c r="C11">
+        <f>-2.903107</f>
+        <v>-2.9031069999999999</v>
+      </c>
+      <c r="D11">
+        <v>1.5807629999999999</v>
+      </c>
+      <c r="F11">
+        <v>5658.7331077667404</v>
+      </c>
+      <c r="G11">
+        <v>-2.9031233502152598</v>
+      </c>
+      <c r="H11">
+        <v>1.5807197390042</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="4"/>
+        <v>3.2008233259148255E-2</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>1.635021525991931E-5</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>4.3260995799876412E-5</v>
+      </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="B12">
+        <v>5658.7305619999997</v>
+      </c>
+      <c r="C12">
+        <v>-2.9265819999999998</v>
+      </c>
+      <c r="D12">
+        <v>1.577035</v>
+      </c>
+      <c r="F12">
+        <v>5658.714661</v>
+      </c>
+      <c r="G12">
+        <v>-2.9265991429767602</v>
+      </c>
+      <c r="H12">
+        <v>1.57699090984538</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="4"/>
+        <v>1.5900999999757914E-2</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>1.7142976760364803E-5</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>4.4090154619924604E-5</v>
+      </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
+      </c>
+      <c r="B13">
+        <v>5659.2853329999998</v>
+      </c>
+      <c r="C13">
+        <v>-2.9302920000000001</v>
+      </c>
+      <c r="D13">
+        <v>1.6004750000000001</v>
+      </c>
+      <c r="F13">
+        <v>5659.2690310452099</v>
+      </c>
+      <c r="G13">
+        <v>-2.9303066602520902</v>
+      </c>
+      <c r="H13">
+        <v>1.6004338450386499</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="4"/>
+        <v>1.6301954789923911E-2</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>1.4660252090070713E-5</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>4.115496135015384E-5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>